--- a/downloads/loesungen/10_Projekte_3NF_Loesung.xlsx
+++ b/downloads/loesungen/10_Projekte_3NF_Loesung.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER" sheetId="1" r:id="R0cd6773c54974f62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABTEILUNG" sheetId="2" r:id="Rfea2eed650754d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJEKT" sheetId="3" r:id="R5e2d87a2122c4b19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER_PROJEKT" sheetId="4" r:id="Ra824181e04ed4215"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER" sheetId="1" r:id="R0577c1b34fa34cad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABTEILUNG" sheetId="2" r:id="R55de4eb76dd845cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJEKT" sheetId="3" r:id="R0d4a051e371a4e68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER_PROJEKT" sheetId="4" r:id="Rfedea25fc22c4b51"/>
   </x:sheets>
 </x:workbook>
 </file>
